--- a/artfynd/A 30324-2022 artfynd.xlsx
+++ b/artfynd/A 30324-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 30324-2022 artfynd.xlsx
+++ b/artfynd/A 30324-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1016,6 +1016,117 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>114694931</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57888</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>runt Kaunisvaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>860066</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7502558</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2019-06-17</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2019-06-17</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>Ulf Sperens</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Ulf Sperens</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 30324-2022 artfynd.xlsx
+++ b/artfynd/A 30324-2022 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>114694931</v>
+        <v>114694839</v>
       </c>
       <c r="B2" t="n">
-        <v>57916</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,26 +686,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103044</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
           <t>1</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hona</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -755,6 +755,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-06-17</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>hona</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,12 +794,7 @@
         <v>114694934</v>
       </c>
       <c r="B3" t="n">
-        <v>57680</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58388</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,15 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>114694839</v>
+        <v>114694931</v>
       </c>
       <c r="B4" t="n">
-        <v>56478</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58636</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -913,31 +908,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>103044</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hona</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -982,11 +972,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2019-06-17</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>hona</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 30324-2022 artfynd.xlsx
+++ b/artfynd/A 30324-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>114694934</v>
+        <v>134752647</v>
       </c>
       <c r="B3" t="n">
-        <v>58388</v>
+        <v>57386</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103001</v>
+        <v>102954</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -824,16 +824,21 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>runt Kaunisvaara, Nb</t>
+          <t>Kaunisvaara, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>860067</v>
+        <v>859543</v>
       </c>
       <c r="R3" t="n">
-        <v>7502558</v>
+        <v>7502725</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,12 +865,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2019-06-17</t>
+          <t>2024-06-01</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>05:19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2019-06-17</t>
+          <t>2024-06-01</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>05:19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,11 +892,6 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>Ulf Sperens</t>
-        </is>
-      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
@@ -890,39 +900,39 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ulf Sperens</t>
+          <t>Via Elin Lindmark</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>114694931</v>
+        <v>114694934</v>
       </c>
       <c r="B4" t="n">
-        <v>58636</v>
+        <v>58388</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103044</v>
+        <v>103001</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1000,6 +1010,112 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>114694931</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>runt Kaunisvaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>860067</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7502558</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2019-06-17</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2019-06-17</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>Ulf Sperens</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Ulf Sperens</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 30324-2022 artfynd.xlsx
+++ b/artfynd/A 30324-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114694839</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134752647</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1010,6 +1025,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114694934</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1116,8 +1136,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114694931</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>